--- a/DocBusinessThienAn/KPI/2026.10_KPI_DatHoangQuy.xlsx
+++ b/DocBusinessThienAn/KPI/2026.10_KPI_DatHoangQuy.xlsx
@@ -1598,6 +1598,8 @@
   </si>
   <si>
     <t>- Triển khai cơ chế gửi nối đuôi dữ liệu và gửi tức thì khi có dữ liệu mới
+- Xử lý luồng gửi dữ liệu: lấy dữ liệu từ CSDL và chuyển đổi đúng cấu trúc đối tác yêu cầu
+- Tự động đóng gói và ghi file dữ liệu gửi đi để lưu trữ làm bằng chứng đối soát
 - Chuẩn hóa luồng log cha - con và theo dõi fix bug kiểm thử F16</t>
   </si>
   <si>
@@ -1607,8 +1609,11 @@
     <t>https://wework.base.vn/tasks?task=11004386</t>
   </si>
   <si>
-    <t>- Xây dựng API và cơ chế phân quyền VideoWall theo người dùng, tổ chức và ô màn hình
-- Phát triển Worker Service giao tiếp thiết bị qua ISAPI/NATS và form WPF test thiết bị</t>
+    <t>- Nghiên cứu tài liệu chuẩn giao tiếp ISAPI của thiết bị điều khiển màn hình
+- Xây dựng API và cơ chế phân quyền VideoWall theo người dùng, tổ chức và ô màn hình
+- Phát triển Worker Service giao tiếp thiết bị qua ISAPI/NATS
+- Xây dựng form WPF test thiết bị
+- Trực tiếp ra site kiểm thử thiết bị (2 ngày): kiểm tra kết nối phần cứng và điều khiển màn hình tại hiện trường</t>
   </si>
   <si>
     <t>2026-10</t>
@@ -3800,7 +3805,7 @@
     <xf numFmtId="1" fontId="7" fillId="13" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="80" xfId="2" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="80" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="80" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10426,7 +10431,7 @@
         <v>(41)</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="122" customFormat="1" ht="108.9" customHeight="1">
+    <row r="13" spans="1:41" s="122" customFormat="1" ht="115" customHeight="1">
       <c r="A13" s="137">
         <v>1</v>
       </c>
@@ -10449,10 +10454,10 @@
         <v>69</v>
       </c>
       <c r="H13" s="137">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="I13" s="137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="139">
         <v>1</v>
@@ -10569,7 +10574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:41" s="122" customFormat="1" ht="108.9" customHeight="1">
+    <row r="14" spans="1:41" s="122" customFormat="1" ht="125" customHeight="1">
       <c r="A14" s="137">
         <v>2</v>
       </c>
@@ -10592,10 +10597,10 @@
         <v>69</v>
       </c>
       <c r="H14" s="137">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I14" s="137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="139">
         <v>1</v>
@@ -11213,7 +11218,7 @@
       <c r="G20" s="331"/>
       <c r="H20" s="146">
         <f>SUM(H13:H19)</f>
-        <v>5.5</v>
+        <v>20.5</v>
       </c>
       <c r="I20" s="146">
         <f>SUM(I13:I19)</f>
@@ -11583,6 +11588,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E13" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000003000001}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300"/>
@@ -11719,9 +11725,9 @@
         <v>95</v>
       </c>
       <c r="B6" s="293"/>
-      <c r="C6" s="294">
+      <c r="C6" s="294" t="str">
         <f>'01. Tổng task'!H4</f>
-        <v>0</v>
+        <v>Hoàng Quý Đạt</v>
       </c>
       <c r="D6" s="284"/>
       <c r="E6" s="281" t="s">
@@ -11782,7 +11788,7 @@
       <c r="B8" s="282"/>
       <c r="C8" s="283" t="str">
         <f>'01. Tổng task'!H5</f>
-        <v>2026-08</v>
+        <v>2026-10</v>
       </c>
       <c r="D8" s="284"/>
       <c r="E8" s="285" t="s">
@@ -11880,7 +11886,8 @@
       </c>
       <c r="C12" s="244" t="str">
         <f>P12</f>
-        <v>XD001.1.8 Điều chỉnh giao diện, chức năng liên quan các phân hệ chính</v>
+        <v>[2026] XD001.5.6 Service tích hợp dữ liệu 2
+XD001.6.3. Service tích hợp thiết bị</v>
       </c>
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
@@ -11893,19 +11900,20 @@
       <c r="L12" s="245"/>
       <c r="M12" s="76">
         <f>COUNTIF('01. Tổng task'!$C$13:$C$19,B12)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="76">
         <f>SUMIF('01. Tổng task'!$C$13:$C$19,B12,'01. Tổng task'!$I$13:$I$19)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O12" s="77">
         <f>IFERROR(SUMPRODUCT(('01. Tổng task'!$C$13:$C$19=$B12)*'01. Tổng task'!$I$13:$I$19*'01. Tổng task'!$AF$13:$AF$19)/SUMIF('01. Tổng task'!$C$13:$C$19,$B12,'01. Tổng task'!$I$13:$I$19),0)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12" s="75" t="str">
         <f t="array" ref="P12">IF($B12="","",_xlfn.TEXTJOIN(CHAR(10),TRUE,IF('01. Tổng task'!$C$13:$C$109=$B12,'01. Tổng task'!$D$13:$D$109,"")))</f>
-        <v>XD001.1.8 Điều chỉnh giao diện, chức năng liên quan các phân hệ chính</v>
+        <v>[2026] XD001.5.6 Service tích hợp dữ liệu 2
+XD001.6.3. Service tích hợp thiết bị</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="95.1" customHeight="1">
@@ -11914,11 +11922,11 @@
       </c>
       <c r="B13" s="74" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(INDEX('01. Tổng task'!$C$13:$C$109,MATCH(0,COUNTIF($B$11:B12,'01. Tổng task'!$C$13:$C$109)+IF('01. Tổng task'!$C$13:$C$109="",1,0),0)),"")</f>
-        <v>Xuất sắc</v>
+        <v/>
       </c>
       <c r="C13" s="244" t="str">
         <f>P13</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
@@ -13163,9 +13171,9 @@
       <c r="P62" s="70"/>
     </row>
     <row r="63" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="209">
+      <c r="A63" s="209" t="str">
         <f>IF(C6&lt;&gt;"",C6,"")</f>
-        <v>0</v>
+        <v>Hoàng Quý Đạt</v>
       </c>
       <c r="B63" s="210"/>
       <c r="C63" s="210"/>
